--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Mistral-Small-3.2-24B-Instruct-2506/aae/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Mistral-Small-3.2-24B-Instruct-2506/aae/total_votes_file.xlsx
@@ -433,13 +433,13 @@
         <v>14</v>
       </c>
       <c r="D2">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D3">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="H3">
         <v>426</v>
